--- a/artfynd/A 12240-2025 artfynd.xlsx
+++ b/artfynd/A 12240-2025 artfynd.xlsx
@@ -1753,7 +1753,7 @@
         <v>127027852</v>
       </c>
       <c r="B12" t="n">
-        <v>91699</v>
+        <v>91773</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>127027827</v>
       </c>
       <c r="B13" t="n">
-        <v>98395</v>
+        <v>98470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 12240-2025 artfynd.xlsx
+++ b/artfynd/A 12240-2025 artfynd.xlsx
@@ -1753,7 +1753,7 @@
         <v>127027852</v>
       </c>
       <c r="B12" t="n">
-        <v>91773</v>
+        <v>91779</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>127027827</v>
       </c>
       <c r="B13" t="n">
-        <v>98470</v>
+        <v>98476</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 12240-2025 artfynd.xlsx
+++ b/artfynd/A 12240-2025 artfynd.xlsx
@@ -1753,7 +1753,7 @@
         <v>127027852</v>
       </c>
       <c r="B12" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>127027827</v>
       </c>
       <c r="B13" t="n">
-        <v>98476</v>
+        <v>98477</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 12240-2025 artfynd.xlsx
+++ b/artfynd/A 12240-2025 artfynd.xlsx
@@ -1753,7 +1753,7 @@
         <v>127027852</v>
       </c>
       <c r="B12" t="n">
-        <v>91780</v>
+        <v>91784</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>127027827</v>
       </c>
       <c r="B13" t="n">
-        <v>98477</v>
+        <v>98481</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 12240-2025 artfynd.xlsx
+++ b/artfynd/A 12240-2025 artfynd.xlsx
@@ -1854,7 +1854,7 @@
         <v>127027827</v>
       </c>
       <c r="B13" t="n">
-        <v>98481</v>
+        <v>98482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 12240-2025 artfynd.xlsx
+++ b/artfynd/A 12240-2025 artfynd.xlsx
@@ -1753,7 +1753,7 @@
         <v>127027852</v>
       </c>
       <c r="B12" t="n">
-        <v>91784</v>
+        <v>91786</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>127027827</v>
       </c>
       <c r="B13" t="n">
-        <v>98482</v>
+        <v>98484</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 12240-2025 artfynd.xlsx
+++ b/artfynd/A 12240-2025 artfynd.xlsx
@@ -1753,7 +1753,7 @@
         <v>127027852</v>
       </c>
       <c r="B12" t="n">
-        <v>91786</v>
+        <v>91792</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>127027827</v>
       </c>
       <c r="B13" t="n">
-        <v>98484</v>
+        <v>98490</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 12240-2025 artfynd.xlsx
+++ b/artfynd/A 12240-2025 artfynd.xlsx
@@ -784,12 +784,7 @@
         <v>111822311</v>
       </c>
       <c r="B3" t="n">
-        <v>89049</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91102</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,19 +796,15 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Druvfingersvamp</t>
+          <t>Druvfingersvampar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramaria botrytis</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Pers.:Fr.) Bourdot</t>
-        </is>
-      </c>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -827,7 +818,7 @@
         <v>600968</v>
       </c>
       <c r="R3" t="n">
-        <v>6639577</v>
+        <v>6639576</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -998,12 +989,7 @@
         <v>111822420</v>
       </c>
       <c r="B5" t="n">
-        <v>89100</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,7 +1024,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601035</v>
+        <v>601036</v>
       </c>
       <c r="R5" t="n">
         <v>6639605</v>
@@ -1104,12 +1090,7 @@
         <v>111822290</v>
       </c>
       <c r="B6" t="n">
-        <v>90821</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92924</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1126,12 +1107,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1210,12 +1191,7 @@
         <v>111822345</v>
       </c>
       <c r="B7" t="n">
-        <v>89550</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91617</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,12 +1292,7 @@
         <v>111822435</v>
       </c>
       <c r="B8" t="n">
-        <v>89539</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91606</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1422,12 +1393,7 @@
         <v>111822338</v>
       </c>
       <c r="B9" t="n">
-        <v>89941</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1444,12 +1410,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1638,12 +1604,7 @@
         <v>112516487</v>
       </c>
       <c r="B11" t="n">
-        <v>93442</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96123</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 12240-2025 artfynd.xlsx
+++ b/artfynd/A 12240-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>111822356</v>
       </c>
       <c r="B2" t="n">
-        <v>89539</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91623</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +779,7 @@
         <v>111822311</v>
       </c>
       <c r="B3" t="n">
-        <v>91102</v>
+        <v>91119</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,12 +876,7 @@
         <v>111822405</v>
       </c>
       <c r="B4" t="n">
-        <v>5402</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +979,7 @@
         <v>111822420</v>
       </c>
       <c r="B5" t="n">
-        <v>91149</v>
+        <v>91166</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1090,7 +1080,7 @@
         <v>111822290</v>
       </c>
       <c r="B6" t="n">
-        <v>92924</v>
+        <v>92941</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,7 +1181,7 @@
         <v>111822345</v>
       </c>
       <c r="B7" t="n">
-        <v>91617</v>
+        <v>91634</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1282,7 @@
         <v>111822435</v>
       </c>
       <c r="B8" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1383,7 @@
         <v>111822338</v>
       </c>
       <c r="B9" t="n">
-        <v>91663</v>
+        <v>91680</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,12 +1484,7 @@
         <v>111822253</v>
       </c>
       <c r="B10" t="n">
-        <v>90799</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92939</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,12 +1501,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1604,7 +1589,7 @@
         <v>112516487</v>
       </c>
       <c r="B11" t="n">
-        <v>96123</v>
+        <v>96140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 12240-2025 artfynd.xlsx
+++ b/artfynd/A 12240-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>111822356</v>
       </c>
       <c r="B2" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>111822311</v>
       </c>
       <c r="B3" t="n">
-        <v>91135</v>
+        <v>91137</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>111822420</v>
       </c>
       <c r="B5" t="n">
-        <v>91182</v>
+        <v>91184</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>111822290</v>
       </c>
       <c r="B6" t="n">
-        <v>92957</v>
+        <v>92959</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>111822345</v>
       </c>
       <c r="B7" t="n">
-        <v>91650</v>
+        <v>91652</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>111822435</v>
       </c>
       <c r="B8" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>111822338</v>
       </c>
       <c r="B9" t="n">
-        <v>91696</v>
+        <v>91698</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>111822253</v>
       </c>
       <c r="B10" t="n">
-        <v>92955</v>
+        <v>92957</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>112516487</v>
       </c>
       <c r="B11" t="n">
-        <v>96156</v>
+        <v>96158</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 12240-2025 artfynd.xlsx
+++ b/artfynd/A 12240-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>111822356</v>
       </c>
       <c r="B2" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>111822311</v>
       </c>
       <c r="B3" t="n">
-        <v>91137</v>
+        <v>91224</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>111822420</v>
       </c>
       <c r="B5" t="n">
-        <v>91184</v>
+        <v>91271</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>111822290</v>
       </c>
       <c r="B6" t="n">
-        <v>92959</v>
+        <v>93046</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>111822345</v>
       </c>
       <c r="B7" t="n">
-        <v>91652</v>
+        <v>91739</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         <v>111822435</v>
       </c>
       <c r="B8" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>111822338</v>
       </c>
       <c r="B9" t="n">
-        <v>91698</v>
+        <v>91785</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>111822253</v>
       </c>
       <c r="B10" t="n">
-        <v>92957</v>
+        <v>93044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>112516487</v>
       </c>
       <c r="B11" t="n">
-        <v>96158</v>
+        <v>96245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>127027852</v>
       </c>
       <c r="B12" t="n">
-        <v>91792</v>
+        <v>91773</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>127027827</v>
       </c>
       <c r="B13" t="n">
-        <v>98490</v>
+        <v>98470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 12240-2025 artfynd.xlsx
+++ b/artfynd/A 12240-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>111822356</v>
       </c>
       <c r="B2" t="n">
-        <v>91728</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111822311</v>
+        <v>111822435</v>
       </c>
       <c r="B3" t="n">
-        <v>91224</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,19 +787,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5734</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -810,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600968</v>
+        <v>601046</v>
       </c>
       <c r="R3" t="n">
-        <v>6639576</v>
+        <v>6639647</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -873,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111822405</v>
+        <v>111822345</v>
       </c>
       <c r="B4" t="n">
-        <v>5469</v>
+        <v>91920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -884,28 +888,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101377</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -913,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601012</v>
+        <v>601030</v>
       </c>
       <c r="R4" t="n">
-        <v>6639500</v>
+        <v>6639755</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -976,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111822420</v>
+        <v>127027852</v>
       </c>
       <c r="B5" t="n">
-        <v>91271</v>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5754</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1014,13 +1016,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601036</v>
+        <v>601035</v>
       </c>
       <c r="R5" t="n">
-        <v>6639605</v>
+        <v>6639822</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1044,12 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1077,35 +1079,39 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111822290</v>
+        <v>111822253</v>
       </c>
       <c r="B6" t="n">
-        <v>93046</v>
+        <v>93231</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>1968</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1115,10 +1121,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600941</v>
+        <v>600947</v>
       </c>
       <c r="R6" t="n">
-        <v>6639648</v>
+        <v>6639683</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1178,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111822345</v>
+        <v>112516487</v>
       </c>
       <c r="B7" t="n">
-        <v>91739</v>
+        <v>96437</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,26 +1195,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1205</v>
+        <v>2667</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1216,13 +1231,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601030</v>
+        <v>601014</v>
       </c>
       <c r="R7" t="n">
-        <v>6639755</v>
+        <v>6639557</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1246,12 +1261,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-31</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1279,10 +1294,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111822435</v>
+        <v>111822442</v>
       </c>
       <c r="B8" t="n">
-        <v>91728</v>
+        <v>87375</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1290,21 +1305,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>3739</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1317,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601046</v>
+        <v>601019</v>
       </c>
       <c r="R8" t="n">
-        <v>6639647</v>
+        <v>6639493</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1383,7 +1398,7 @@
         <v>111822338</v>
       </c>
       <c r="B9" t="n">
-        <v>91785</v>
+        <v>91966</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111822253</v>
+        <v>111822420</v>
       </c>
       <c r="B10" t="n">
-        <v>93044</v>
+        <v>91443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,28 +1507,24 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1968</v>
+        <v>5754</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1523,10 +1534,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600947</v>
+        <v>601036</v>
       </c>
       <c r="R10" t="n">
-        <v>6639683</v>
+        <v>6639605</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1586,46 +1597,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112516487</v>
+        <v>111822290</v>
       </c>
       <c r="B11" t="n">
-        <v>96245</v>
+        <v>93233</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2667</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1633,13 +1635,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601014</v>
+        <v>600941</v>
       </c>
       <c r="R11" t="n">
-        <v>6639557</v>
+        <v>6639648</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1663,12 +1665,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1696,32 +1698,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127027852</v>
+        <v>111822458</v>
       </c>
       <c r="B12" t="n">
-        <v>91792</v>
+        <v>80336</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1734,13 +1736,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601035</v>
+        <v>601047</v>
       </c>
       <c r="R12" t="n">
-        <v>6639822</v>
+        <v>6639531</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1764,12 +1766,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1797,10 +1799,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127027827</v>
+        <v>111822465</v>
       </c>
       <c r="B13" t="n">
-        <v>98490</v>
+        <v>80367</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1808,27 +1810,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219874</v>
+        <v>6457</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1836,13 +1837,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601052</v>
+        <v>601047</v>
       </c>
       <c r="R13" t="n">
-        <v>6639666</v>
+        <v>6639531</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1866,12 +1867,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2023-08-31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1896,6 +1897,514 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>111822405</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5471</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>101377</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Stekelbock</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Necydalis major</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långmossen S Turbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>601012</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6639500</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Västerlövsta</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127027827</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långmossen S Turbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>601052</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6639666</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Västerlövsta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>111822506</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långmossen S Turbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>601079</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6639569</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Västerlövsta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>111822545</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Långmossen S Turbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>601086</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6639593</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Västerlövsta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>111822579</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långmossen S Turbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>601148</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6639772</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Västerlövsta</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12240-2025 artfynd.xlsx
+++ b/artfynd/A 12240-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111822356</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111822435</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111822345</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127027852</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111822253</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1291,6 +1321,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112516487</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1392,6 +1427,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111822442</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1493,6 +1533,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111822338</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1594,6 +1639,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111822420</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1695,6 +1745,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111822290</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1796,6 +1851,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111822458</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1897,6 +1957,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111822465</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1998,6 +2063,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111822506</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2099,6 +2169,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111822545</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2202,6 +2277,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111822405</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2304,6 +2384,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127027827</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2405,8 +2490,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111822579</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>